--- a/data/presupuesto/Conciliacion_Final_ETC88.xlsx
+++ b/data/presupuesto/Conciliacion_Final_ETC88.xlsx
@@ -803,7 +803,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>27</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="3816000" cy="2951999"/>
@@ -825,7 +825,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>27</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="3816000" cy="2951999"/>
@@ -1136,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1502,7 +1502,7 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>PENDIENTES (0 abiertos · 1 notas)</t>
+          <t>PENDIENTES (0 abiertos · 2 notas)</t>
         </is>
       </c>
     </row>
@@ -1518,142 +1518,154 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Biblias: las 2 de Camila</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Confirmar con Camila y con Juan Manuel: si ella puso 1,360 de su bolsillo, o se le reembolsa, o se registra como donación en especie (el costo del retiro subiría a 618,429 y la especie a 93,765). La caja y el cuadre con el banco no cambian en ningún caso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>DISTRIBUCIÓN DEL DINERO</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Izquierda: de dónde salió cada peso que entró. Derecha: en qué se fue cada peso que salió de caja.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="14" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
         <is>
           <t>HOJAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>1 Caja</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>entradas por fuente, salidas, balance, banco</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="15" t="inlineStr">
         <is>
-          <t>2 Presupuesto vs costo</t>
+          <t>1 Caja</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>presupuestado → costó → cubierto sin pagar → pagado de caja, por área</t>
+          <t>entradas por fuente, salidas, balance, banco</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
         <is>
-          <t>3 Al costo vs caja</t>
+          <t>2 Presupuesto vs costo</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>qué vale el retiro y qué nos costó; la casa al detalle</t>
+          <t>presupuestado → costó → cubierto sin pagar → pagado de caja, por área</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="15" t="inlineStr">
         <is>
-          <t>4 Base ETC 89</t>
+          <t>3 Al costo vs caja</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>costo real por partida y por persona; recomendaciones para el próximo</t>
+          <t>qué vale el retiro y qué nos costó; la casa al detalle</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="15" t="inlineStr">
         <is>
-          <t>5 Pendientes</t>
+          <t>4 Base ETC 89</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>una sola lista: abiertos, notas, cerrados</t>
+          <t>costo real por partida y por persona; recomendaciones para el próximo</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="15" t="inlineStr">
         <is>
-          <t>6 Ppto oficial vs Sistem</t>
+          <t>5 Pendientes</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>los dos presupuestos por área</t>
+          <t>una sola lista: abiertos, notas, cerrados</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="15" t="inlineStr">
         <is>
-          <t>7–10 Anexos</t>
+          <t>6 Ppto oficial vs Sistem</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Gastos · Donaciones efectivo · Especie · Profondo (con la liquidación de la comisión)</t>
+          <t>los dos presupuestos por área</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="15" t="inlineStr">
         <is>
-          <t>11 Auditoría</t>
+          <t>7–10 Anexos</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>36 verificaciones recalculadas (36 cuadran)</t>
+          <t>Gastos · Donaciones efectivo · Especie · Profondo (con la liquidación de la comisión)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="15" t="inlineStr">
         <is>
-          <t>12 Fuentes y método</t>
+          <t>11 Auditoría</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>de dónde sale cada número y las reglas usadas</t>
+          <t>37 verificaciones recalculadas (37 cuadran)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="15" t="inlineStr">
         <is>
+          <t>12 Fuentes y método</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>de dónde sale cada número y las reglas usadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
           <t>13 Notas por partida</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>la explicación de cada partida del presupuesto</t>
         </is>
@@ -2594,7 +2606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3473,14 +3485,14 @@
       </c>
       <c r="B36" s="39" t="inlineStr">
         <is>
-          <t>Biblias: reembolso 35,360 = proforma 34,000 + 1,360; donaciones etiquetadas "biblia"</t>
+          <t>Biblias: el pago de 35,360 = 52 × 680 exactos</t>
         </is>
       </c>
       <c r="C36" s="17" t="n">
-        <v>16500</v>
+        <v>35360</v>
       </c>
       <c r="D36" s="17" t="n">
-        <v>16500</v>
+        <v>35360</v>
       </c>
       <c r="E36" s="86" t="inlineStr">
         <is>
@@ -3489,7 +3501,7 @@
       </c>
       <c r="F36" s="18" t="inlineStr">
         <is>
-          <t>Roosbert, Pamela Nivar, Carol, Kharla, Wirna</t>
+          <t>el presupuesto tenía 50 (34,000); las 2 de más (1,360) son las que iba a pagar Camila</t>
         </is>
       </c>
     </row>
@@ -3499,14 +3511,14 @@
       </c>
       <c r="B37" s="39" t="inlineStr">
         <is>
-          <t>Donaciones que requieren nota: el depósito sin dueño y la de Yendry sin captura</t>
+          <t>Biblias: donaciones en efectivo etiquetadas "biblia"</t>
         </is>
       </c>
       <c r="C37" s="17" t="n">
-        <v>2000</v>
+        <v>16500</v>
       </c>
       <c r="D37" s="17" t="n">
-        <v>2000</v>
+        <v>16500</v>
       </c>
       <c r="E37" s="86" t="inlineStr">
         <is>
@@ -3515,7 +3527,7 @@
       </c>
       <c r="F37" s="18" t="inlineStr">
         <is>
-          <t>las de Wilfrid y Johan se ubicaron: ya no llevan nota</t>
+          <t>Roosbert, Pamela Nivar, Carol, Kharla, Wirna</t>
         </is>
       </c>
     </row>
@@ -3525,21 +3537,25 @@
       </c>
       <c r="B38" s="39" t="inlineStr">
         <is>
-          <t>Costo del retiro = caja + especie + cortesías (8 × 500 + 2 × 2,360)</t>
+          <t>Donaciones que requieren nota: el depósito sin dueño y la de Yendry sin captura</t>
         </is>
       </c>
       <c r="C38" s="17" t="n">
-        <v>617069</v>
+        <v>2000</v>
       </c>
       <c r="D38" s="17" t="n">
-        <v>617069</v>
+        <v>2000</v>
       </c>
       <c r="E38" s="86" t="inlineStr">
         <is>
           <t>Cuadra</t>
         </is>
       </c>
-      <c r="F38" s="18" t="inlineStr"/>
+      <c r="F38" s="18" t="inlineStr">
+        <is>
+          <t>las de Wilfrid y Johan se ubicaron: ya no llevan nota</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="85" t="n">
@@ -3547,26 +3563,48 @@
       </c>
       <c r="B39" s="39" t="inlineStr">
         <is>
+          <t>Costo del retiro = caja + especie + cortesías (8 × 500 + 2 × 2,360)</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="n">
+        <v>617069</v>
+      </c>
+      <c r="D39" s="17" t="n">
+        <v>617069</v>
+      </c>
+      <c r="E39" s="86" t="inlineStr">
+        <is>
+          <t>Cuadra</t>
+        </is>
+      </c>
+      <c r="F39" s="18" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="85" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="39" t="inlineStr">
+        <is>
           <t>Apoyo total donado = efectivo + especie</t>
         </is>
       </c>
-      <c r="C39" s="17" t="n">
+      <c r="C40" s="17" t="n">
         <v>247426</v>
       </c>
-      <c r="D39" s="17" t="n">
+      <c r="D40" s="17" t="n">
         <v>247426</v>
       </c>
-      <c r="E39" s="86" t="inlineStr">
+      <c r="E40" s="86" t="inlineStr">
         <is>
           <t>Cuadra</t>
         </is>
       </c>
-      <c r="F39" s="18" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>36 de 36 verificaciones cuadran</t>
+      <c r="F40" s="18" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>37 de 37 verificaciones cuadran</t>
         </is>
       </c>
     </row>
@@ -4062,12 +4100,12 @@
       </c>
       <c r="B12" s="39" t="inlineStr">
         <is>
-          <t>Biblias (50 × 680)</t>
+          <t>Biblias (52 × 680)</t>
         </is>
       </c>
       <c r="C12" s="39" t="inlineStr">
         <is>
-          <t>Reembolso a JM (19/08): proforma Paulinas 34,000 + 1,360. Donaciones en efectivo etiquetadas "biblia": 16,500</t>
+          <t>Se pidieron 52 y el grupo pagó las 52: 52 × 680 = 35,360 exactos (reembolso a JM, 19/08). El presupuesto oficial solo contemplaba 50 (34,000) porque 2 las pagaría Camila; esas 2 (1,360) quedaron dentro de lo que pagó el grupo. Financiadas en parte por 16,500 de donaciones en efectivo etiquetadas "biblia"</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5130,7 @@
     <row r="15" outlineLevel="1">
       <c r="B15" s="39" t="inlineStr">
         <is>
-          <t>Biblias (50 × 680)</t>
+          <t>Biblias (52 × 680)</t>
         </is>
       </c>
       <c r="C15" s="17" t="n">
@@ -6580,7 +6618,7 @@
       </c>
       <c r="B12" s="39" t="inlineStr">
         <is>
-          <t>Biblias (50 × 680)</t>
+          <t>Biblias (52 × 680)</t>
         </is>
       </c>
       <c r="C12" s="17" t="n">
@@ -7585,7 +7623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7747,22 +7785,26 @@
       <c r="D9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="69" t="inlineStr">
-        <is>
-          <t>CERRADO</t>
+      <c r="A10" s="59" t="inlineStr">
+        <is>
+          <t>NOTA</t>
         </is>
       </c>
       <c r="B10" s="70" t="inlineStr">
         <is>
-          <t>Impresión de libretas 1,260</t>
+          <t>Biblias: las 2 de Camila</t>
         </is>
       </c>
       <c r="C10" s="39" t="inlineStr">
         <is>
-          <t>El presupuesto operativo la marcaba "donado por guías" en la columna equivocada, por eso no sumaba. Sumada a la especie por confirmación del director (11-sep).</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr"/>
+          <t>Se pidieron 52 biblias y el grupo pagó las 52: el reembolso a JM del 19/08 es 35,360 = 52 × 680 exactos. El presupuesto solo contemplaba 50 (34,000) porque 2 las pagaría Camila Fernández; esas 2 quedaron dentro de lo que pagó el grupo. En las 49 donaciones en efectivo no hay ningún aporte suyo ni ningún movimiento de 1,360, y en la especie solo figura por los separadores de libros (750).</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>Confirmar con Camila y con Juan Manuel: si ella puso 1,360 de su bolsillo, o se le reembolsa, o se registra como donación en especie (el costo del retiro subiría a 618,429 y la especie a 93,765). La caja y el cuadre con el banco no cambian en ningún caso.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="69" t="inlineStr">
@@ -7772,12 +7814,12 @@
       </c>
       <c r="B11" s="70" t="inlineStr">
         <is>
-          <t>Uso de los 34,337 en cuentas</t>
+          <t>Impresión de libretas 1,260</t>
         </is>
       </c>
       <c r="C11" s="39" t="inlineStr">
         <is>
-          <t>La dirección lo expondrá en la actividad de cierre (evaluación) del ETC 88 para decidirlo con el equipo (11-sep).</t>
+          <t>El presupuesto operativo la marcaba "donado por guías" en la columna equivocada, por eso no sumaba. Sumada a la especie por confirmación del director (11-sep).</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr"/>
@@ -7790,12 +7832,12 @@
       </c>
       <c r="B12" s="70" t="inlineStr">
         <is>
-          <t>Profondo: liquidación de la comisión</t>
+          <t>Uso de los 34,337 en cuentas</t>
         </is>
       </c>
       <c r="C12" s="39" t="inlineStr">
         <is>
-          <t>Bruto 154,420: 680.5 boletas pagadas × 200 = 136,100 + venta de comida y helados 18,320. Premios 19,900 (aire acondicionado 16,900 + abanico de torre 3,000). Neto del informe 134,520; entregado a finanzas 135,866.40: los 1,346.40 adicionales son ventas de helados posteriores al informe (director).</t>
+          <t>La dirección lo expondrá en la actividad de cierre (evaluación) del ETC 88 para decidirlo con el equipo (11-sep).</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr"/>
@@ -7808,12 +7850,12 @@
       </c>
       <c r="B13" s="70" t="inlineStr">
         <is>
-          <t>Pagaron y no fueron</t>
+          <t>Profondo: liquidación de la comisión</t>
         </is>
       </c>
       <c r="C13" s="39" t="inlineStr">
         <is>
-          <t>Verificado nombre por nombre contra la lista de pagos del director (10-sep, 57 líneas), el registro de cuotas y las 49 donaciones. Equipo: Mary Carmen Ramírez pagó y no asistió; sus 2,000 están dentro de los 98,000. Participantes: los 46 que pagaron están todos identificados con nombre y ninguno figura como ausente. Boris pagó, no fue, se le devolvió una parte y el neto de 1,500 entró como donación a nombre de Jonathan Medina (31/08): su dinero NO está en los 156,800. De Amanda Rivera no hay ningún pago en ninguna fuente; solo aparece en el formulario de junio como invitada de Pamela Colón y Roselyn Quiroz. Los únicos abonos de 500 de la lista son de Melany Ceverino y Erilis Polanco, ambas personas que sí asistieron.</t>
+          <t>Bruto 154,420: 680.5 boletas pagadas × 200 = 136,100 + venta de comida y helados 18,320. Premios 19,900 (aire acondicionado 16,900 + abanico de torre 3,000). Neto del informe 134,520; entregado a finanzas 135,866.40: los 1,346.40 adicionales son ventas de helados posteriores al informe (director).</t>
         </is>
       </c>
       <c r="D13" s="18" t="inlineStr"/>
@@ -7826,12 +7868,12 @@
       </c>
       <c r="B14" s="70" t="inlineStr">
         <is>
-          <t>Presupuesto oficial</t>
+          <t>Pagaron y no fueron</t>
         </is>
       </c>
       <c r="C14" s="39" t="inlineStr">
         <is>
-          <t>Declarado OFICIAL el de 11-Ago (596,249.56, costo completo, tarifa real de la casa). El Sistem (512,859.56) es la referencia operativa del tablero.</t>
+          <t>Verificado nombre por nombre contra la lista de pagos del director (10-sep, 57 líneas), el registro de cuotas y las 49 donaciones. Equipo: Mary Carmen Ramírez pagó y no asistió; sus 2,000 están dentro de los 98,000. Participantes: los 46 que pagaron están todos identificados con nombre y ninguno figura como ausente. Boris pagó, no fue, se le devolvió una parte y el neto de 1,500 entró como donación a nombre de Jonathan Medina (31/08): su dinero NO está en los 156,800. De Amanda Rivera no hay ningún pago en ninguna fuente; solo aparece en el formulario de junio como invitada de Pamela Colón y Roselyn Quiroz. Los únicos abonos de 500 de la lista son de Melany Ceverino y Erilis Polanco, ambas personas que sí asistieron.</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr"/>
@@ -7844,19 +7886,15 @@
       </c>
       <c r="B15" s="70" t="inlineStr">
         <is>
-          <t>Pago a JM 37,500</t>
+          <t>Presupuesto oficial</t>
         </is>
       </c>
       <c r="C15" s="39" t="inlineStr">
         <is>
-          <t>Desglosado en la hoja de Gastos: transporte 2ª mitad 17,500 (10,000 + 7,500) + desvío 10,000 + ofrenda P. Héctor 10,000.</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>Registrar el desglose en el tablero.</t>
-        </is>
-      </c>
+          <t>Declarado OFICIAL el de 11-Ago (596,249.56, costo completo, tarifa real de la casa). El Sistem (512,859.56) es la referencia operativa del tablero.</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="69" t="inlineStr">
@@ -7866,15 +7904,19 @@
       </c>
       <c r="B16" s="70" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Pago a JM 37,500</t>
         </is>
       </c>
       <c r="C16" s="39" t="inlineStr">
         <is>
-          <t>Fuimos 99, facturadas 97. Cortesías: el padre y la sor (la del director cedida a la sor). Jueves: 27 personas, 19 pagaron 500, 8 sin cobro. Habitaciones de pequeños grupos: 900 × 2 noches. Total 240,220 = avance 23,600 + final 216,620.</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr"/>
+          <t>Desglosado en la hoja de Gastos: transporte 2ª mitad 17,500 (10,000 + 7,500) + desvío 10,000 + ofrenda P. Héctor 10,000.</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>Registrar el desglose en el tablero.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="69" t="inlineStr">
@@ -7884,12 +7926,12 @@
       </c>
       <c r="B17" s="70" t="inlineStr">
         <is>
-          <t>Bizcocho y helados</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="C17" s="39" t="inlineStr">
         <is>
-          <t>Bizcocho de bienvenida 6,000 (10/09, no presupuestado). El bizcocho de la dinámica (ppto Cocina 1,500) se cambió por helados: 1,740 (07/09). La venta de helados del profondo es ingreso, no costo.</t>
+          <t>Fuimos 99, facturadas 97. Cortesías: el padre y la sor (la del director cedida a la sor). Jueves: 27 personas, 19 pagaron 500, 8 sin cobro. Habitaciones de pequeños grupos: 900 × 2 noches. Total 240,220 = avance 23,600 + final 216,620.</t>
         </is>
       </c>
       <c r="D17" s="18" t="inlineStr"/>
@@ -7902,12 +7944,12 @@
       </c>
       <c r="B18" s="70" t="inlineStr">
         <is>
-          <t>Lapiceros e insumos de misa</t>
+          <t>Bizcocho y helados</t>
         </is>
       </c>
       <c r="C18" s="39" t="inlineStr">
         <is>
-          <t>Caja de lapiceros (650) donada; insumos de misa (3,000) asumidos por Jonathan Medina y Fernando Cordero. Ambos en la especie.</t>
+          <t>Bizcocho de bienvenida 6,000 (10/09, no presupuestado). El bizcocho de la dinámica (ppto Cocina 1,500) se cambió por helados: 1,740 (07/09). La venta de helados del profondo es ingreso, no costo.</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr"/>
@@ -7920,12 +7962,12 @@
       </c>
       <c r="B19" s="70" t="inlineStr">
         <is>
-          <t>Impresiones de guías</t>
+          <t>Lapiceros e insumos de misa</t>
         </is>
       </c>
       <c r="C19" s="39" t="inlineStr">
         <is>
-          <t>Mochilas (3,600, pagadas) e "impresiones diversas" (3,600, donadas por Darianny) son trabajos distintos. No hay doble conteo.</t>
+          <t>Caja de lapiceros (650) donada; insumos de misa (3,000) asumidos por Jonathan Medina y Fernando Cordero. Ambos en la especie.</t>
         </is>
       </c>
       <c r="D19" s="18" t="inlineStr"/>
@@ -7938,12 +7980,12 @@
       </c>
       <c r="B20" s="70" t="inlineStr">
         <is>
-          <t>Priscila</t>
+          <t>Impresiones de guías</t>
         </is>
       </c>
       <c r="C20" s="39" t="inlineStr">
         <is>
-          <t>Donó materiales (7,340) y recibió 2,000 en efectivo (21/07). Donación neta 5,340; la especie ya lo descuenta.</t>
+          <t>Mochilas (3,600, pagadas) e "impresiones diversas" (3,600, donadas por Darianny) son trabajos distintos. No hay doble conteo.</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr"/>
@@ -7956,37 +7998,37 @@
       </c>
       <c r="B21" s="70" t="inlineStr">
         <is>
+          <t>Priscila</t>
+        </is>
+      </c>
+      <c r="C21" s="39" t="inlineStr">
+        <is>
+          <t>Donó materiales (7,340) y recibió 2,000 en efectivo (21/07). Donación neta 5,340; la especie ya lo descuenta.</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="69" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="B22" s="70" t="inlineStr">
+        <is>
           <t>Balance 117,611 de la hoja General</t>
         </is>
       </c>
-      <c r="C21" s="39" t="inlineStr">
+      <c r="C22" s="39" t="inlineStr">
         <is>
           <t>Cifra escrita a mano hacia el 11-ago, antes del retiro. No es un segundo balance. El oficial es 36,543.40 → real 34,337.</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D22" s="18" t="inlineStr">
         <is>
           <t>Borrar o anotar esa cifra en la hoja de presupuesto.</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="71" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="B22" s="70" t="inlineStr">
-        <is>
-          <t>Especie</t>
-        </is>
-      </c>
-      <c r="C22" s="39" t="inlineStr">
-        <is>
-          <t>Total 92,405: la hoja de presupuesto solo tenía marcados 30,301 (marcas sin actualizar). Peces (36,000), decoración (10,300), Bono Olé (4,588), insumos de misa (3,000), oficina, lapiceros y cocina no estaban marcados.</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="71" t="inlineStr">
@@ -7996,12 +8038,12 @@
       </c>
       <c r="B23" s="70" t="inlineStr">
         <is>
-          <t>Oficina</t>
+          <t>Especie</t>
         </is>
       </c>
       <c r="C23" s="39" t="inlineStr">
         <is>
-          <t>Costo real 5,306.11 asumido por los directores; en la especie se valora a ppto (2,300) por instrucción del director. Solo informativo.</t>
+          <t>Total 92,405: la hoja de presupuesto solo tenía marcados 30,301 (marcas sin actualizar). Peces (36,000), decoración (10,300), Bono Olé (4,588), insumos de misa (3,000), oficina, lapiceros y cocina no estaban marcados.</t>
         </is>
       </c>
       <c r="D23" s="18" t="inlineStr"/>
@@ -8014,12 +8056,12 @@
       </c>
       <c r="B24" s="70" t="inlineStr">
         <is>
-          <t>Presupuestos "Tentativo"</t>
+          <t>Oficina</t>
         </is>
       </c>
       <c r="C24" s="39" t="inlineStr">
         <is>
-          <t>Ambos quedaron marcados "Tentativo — sujeto a ajustes" (2/7/2026). Lección ETC 89: cerrar el presupuesto formalmente antes del retiro y marcar las donaciones en especie al recibirlas.</t>
+          <t>Costo real 5,306.11 asumido por los directores; en la especie se valora a ppto (2,300) por instrucción del director. Solo informativo.</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr"/>
@@ -8032,15 +8074,33 @@
       </c>
       <c r="B25" s="70" t="inlineStr">
         <is>
+          <t>Presupuestos "Tentativo"</t>
+        </is>
+      </c>
+      <c r="C25" s="39" t="inlineStr">
+        <is>
+          <t>Ambos quedaron marcados "Tentativo — sujeto a ajustes" (2/7/2026). Lección ETC 89: cerrar el presupuesto formalmente antes del retiro y marcar las donaciones en especie al recibirlas.</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="71" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="B26" s="70" t="inlineStr">
+        <is>
           <t>Tablero público</t>
         </is>
       </c>
-      <c r="C25" s="39" t="inlineStr">
+      <c r="C26" s="39" t="inlineStr">
         <is>
           <t>Vista pública: corregido el ancho de las tarjetas y añadida la tarjeta de Profondo (corrección entregada). Falta publicarla.</t>
         </is>
       </c>
-      <c r="D25" s="18" t="inlineStr">
+      <c r="D26" s="18" t="inlineStr">
         <is>
           <t>Publicar la corrección en el tablero.</t>
         </is>
@@ -8518,7 +8578,7 @@
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>Reembolso. Proforma Paulinas 34,000 + 1,360</t>
+          <t>Reembolso a JM. 52 biblias × 680 = 35,360 exactos. El presupuesto solo tenía 50 (34,000): las 2 de más (1,360) son las que figuraban como 'las pagaría Camila' y terminaron dentro de lo que pagó el grupo</t>
         </is>
       </c>
     </row>

--- a/data/presupuesto/Conciliacion_Final_ETC88.xlsx
+++ b/data/presupuesto/Conciliacion_Final_ETC88.xlsx
@@ -803,7 +803,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="3816000" cy="2951999"/>
@@ -825,7 +825,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="3816000" cy="2951999"/>
@@ -1136,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1502,7 +1502,7 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>PENDIENTES (0 abiertos · 2 notas)</t>
+          <t>PENDIENTES (0 abiertos · 3 notas)</t>
         </is>
       </c>
     </row>
@@ -1530,142 +1530,154 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>Habitaciones de pequeños grupos: 400 sin explicar</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Una línea de la factura de la casa lo cierra. No afecta ningún total: lo pagado es lo pagado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>DISTRIBUCIÓN DEL DINERO</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Izquierda: de dónde salió cada peso que entró. Derecha: en qué se fue cada peso que salió de caja.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="14" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>HOJAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>1 Caja</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>entradas por fuente, salidas, balance, banco</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
         <is>
-          <t>2 Presupuesto vs costo</t>
+          <t>1 Caja</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>presupuestado → costó → cubierto sin pagar → pagado de caja, por área</t>
+          <t>entradas por fuente, salidas, balance, banco</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="15" t="inlineStr">
         <is>
-          <t>3 Al costo vs caja</t>
+          <t>2 Presupuesto vs costo</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>qué vale el retiro y qué nos costó; la casa al detalle</t>
+          <t>presupuestado → costó → cubierto sin pagar → pagado de caja, por área</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="15" t="inlineStr">
         <is>
-          <t>4 Base ETC 89</t>
+          <t>3 Al costo vs caja</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>costo real por partida y por persona; recomendaciones para el próximo</t>
+          <t>qué vale el retiro y qué nos costó; la casa al detalle</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="15" t="inlineStr">
         <is>
-          <t>5 Pendientes</t>
+          <t>4 Base ETC 89</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>una sola lista: abiertos, notas, cerrados</t>
+          <t>costo real por partida y por persona; recomendaciones para el próximo</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="15" t="inlineStr">
         <is>
-          <t>6 Ppto oficial vs Sistem</t>
+          <t>5 Pendientes</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>los dos presupuestos por área</t>
+          <t>una sola lista: abiertos, notas, cerrados</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="15" t="inlineStr">
         <is>
-          <t>7–10 Anexos</t>
+          <t>6 Ppto oficial vs Sistem</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Gastos · Donaciones efectivo · Especie · Profondo (con la liquidación de la comisión)</t>
+          <t>los dos presupuestos por área</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="15" t="inlineStr">
         <is>
-          <t>11 Auditoría</t>
+          <t>7–10 Anexos</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>37 verificaciones recalculadas (37 cuadran)</t>
+          <t>Gastos · Donaciones efectivo · Especie · Profondo (con la liquidación de la comisión)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="15" t="inlineStr">
         <is>
-          <t>12 Fuentes y método</t>
+          <t>11 Auditoría</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>de dónde sale cada número y las reglas usadas</t>
+          <t>37 verificaciones recalculadas (37 cuadran)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="15" t="inlineStr">
         <is>
+          <t>12 Fuentes y método</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>de dónde sale cada número y las reglas usadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="inlineStr">
+        <is>
           <t>13 Notas por partida</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>la explicación de cada partida del presupuesto</t>
         </is>
@@ -4037,7 +4049,7 @@
       </c>
       <c r="C8" s="39" t="inlineStr">
         <is>
-          <t>Tarifa inferida: 900/noche × 2 noches = 1,800 (240,220 − 228,920 − 9,500)</t>
+          <t>Los 1,800 son firmes: es lo que queda del pago a la casa tras el hospedaje y el jueves (240,220 − 228,920 − 9,500). La tarifa de 900/noche es INFERIDA de ahí. El desglose verbal del 10-sep (700 × 2 noches + 800 de una habitación extra = 2,200) daría 400 más de lo que se pagó: diferencia sin explicar, pendiente de la factura de la casa</t>
         </is>
       </c>
     </row>
@@ -6200,7 +6212,7 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>tarifa inferida 900/noche</t>
+          <t>monto firme; tarifa inferida 900/noche. El desglose verbal (700 × 2 + 800 = 2,200) daría 400 más</t>
         </is>
       </c>
     </row>
@@ -7623,7 +7635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7807,22 +7819,26 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="69" t="inlineStr">
-        <is>
-          <t>CERRADO</t>
+      <c r="A11" s="59" t="inlineStr">
+        <is>
+          <t>NOTA</t>
         </is>
       </c>
       <c r="B11" s="70" t="inlineStr">
         <is>
-          <t>Impresión de libretas 1,260</t>
+          <t>Habitaciones de pequeños grupos: 400 sin explicar</t>
         </is>
       </c>
       <c r="C11" s="39" t="inlineStr">
         <is>
-          <t>El presupuesto operativo la marcaba "donado por guías" en la columna equivocada, por eso no sumaba. Sumada a la especie por confirmación del director (11-sep).</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr"/>
+          <t>Los 1,800 son firmes: es lo que queda del pago a la casa tras el hospedaje (228,920) y el jueves (9,500). La tarifa de 900/noche está inferida de ahí. El desglose que dio la dirección el 10-sep (700 × 2 noches + 800 de una habitación extra) suma 2,200, o sea 400 más de lo que la casa cobró.</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>Una línea de la factura de la casa lo cierra. No afecta ningún total: lo pagado es lo pagado.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="69" t="inlineStr">
@@ -7832,12 +7848,12 @@
       </c>
       <c r="B12" s="70" t="inlineStr">
         <is>
-          <t>Uso de los 34,337 en cuentas</t>
+          <t>Impresión de libretas 1,260</t>
         </is>
       </c>
       <c r="C12" s="39" t="inlineStr">
         <is>
-          <t>La dirección lo expondrá en la actividad de cierre (evaluación) del ETC 88 para decidirlo con el equipo (11-sep).</t>
+          <t>El presupuesto operativo la marcaba "donado por guías" en la columna equivocada, por eso no sumaba. Sumada a la especie por confirmación del director (11-sep).</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr"/>
@@ -7850,12 +7866,12 @@
       </c>
       <c r="B13" s="70" t="inlineStr">
         <is>
-          <t>Profondo: liquidación de la comisión</t>
+          <t>Uso de los 34,337 en cuentas</t>
         </is>
       </c>
       <c r="C13" s="39" t="inlineStr">
         <is>
-          <t>Bruto 154,420: 680.5 boletas pagadas × 200 = 136,100 + venta de comida y helados 18,320. Premios 19,900 (aire acondicionado 16,900 + abanico de torre 3,000). Neto del informe 134,520; entregado a finanzas 135,866.40: los 1,346.40 adicionales son ventas de helados posteriores al informe (director).</t>
+          <t>La dirección lo expondrá en la actividad de cierre (evaluación) del ETC 88 para decidirlo con el equipo (11-sep).</t>
         </is>
       </c>
       <c r="D13" s="18" t="inlineStr"/>
@@ -7868,12 +7884,12 @@
       </c>
       <c r="B14" s="70" t="inlineStr">
         <is>
-          <t>Pagaron y no fueron</t>
+          <t>Profondo: liquidación de la comisión</t>
         </is>
       </c>
       <c r="C14" s="39" t="inlineStr">
         <is>
-          <t>Verificado nombre por nombre contra la lista de pagos del director (10-sep, 57 líneas), el registro de cuotas y las 49 donaciones. Equipo: Mary Carmen Ramírez pagó y no asistió; sus 2,000 están dentro de los 98,000. Participantes: los 46 que pagaron están todos identificados con nombre y ninguno figura como ausente. Boris pagó, no fue, se le devolvió una parte y el neto de 1,500 entró como donación a nombre de Jonathan Medina (31/08): su dinero NO está en los 156,800. De Amanda Rivera no hay ningún pago en ninguna fuente; solo aparece en el formulario de junio como invitada de Pamela Colón y Roselyn Quiroz. Los únicos abonos de 500 de la lista son de Melany Ceverino y Erilis Polanco, ambas personas que sí asistieron.</t>
+          <t>Bruto 154,420: 680.5 boletas pagadas × 200 = 136,100 + venta de comida y helados 18,320. Premios 19,900 (aire acondicionado 16,900 + abanico de torre 3,000). Neto del informe 134,520; entregado a finanzas 135,866.40: los 1,346.40 adicionales son ventas de helados posteriores al informe (director).</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr"/>
@@ -7886,12 +7902,12 @@
       </c>
       <c r="B15" s="70" t="inlineStr">
         <is>
-          <t>Presupuesto oficial</t>
+          <t>Pagaron y no fueron</t>
         </is>
       </c>
       <c r="C15" s="39" t="inlineStr">
         <is>
-          <t>Declarado OFICIAL el de 11-Ago (596,249.56, costo completo, tarifa real de la casa). El Sistem (512,859.56) es la referencia operativa del tablero.</t>
+          <t>Verificado nombre por nombre contra la lista de pagos del director (10-sep, 57 líneas), el registro de cuotas y las 49 donaciones. Equipo: Mary Carmen Ramírez pagó y no asistió; sus 2,000 están dentro de los 98,000. Participantes: los 46 que pagaron están todos identificados con nombre y ninguno figura como ausente. Boris pagó, no fue, se le devolvió una parte y el neto de 1,500 entró como donación a nombre de Jonathan Medina (31/08): su dinero NO está en los 156,800. De Amanda Rivera no hay ningún pago en ninguna fuente; solo aparece en el formulario de junio como invitada de Pamela Colón y Roselyn Quiroz. Los únicos abonos de 500 de la lista son de Melany Ceverino y Erilis Polanco, ambas personas que sí asistieron.</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr"/>
@@ -7904,19 +7920,15 @@
       </c>
       <c r="B16" s="70" t="inlineStr">
         <is>
-          <t>Pago a JM 37,500</t>
+          <t>Presupuesto oficial</t>
         </is>
       </c>
       <c r="C16" s="39" t="inlineStr">
         <is>
-          <t>Desglosado en la hoja de Gastos: transporte 2ª mitad 17,500 (10,000 + 7,500) + desvío 10,000 + ofrenda P. Héctor 10,000.</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>Registrar el desglose en el tablero.</t>
-        </is>
-      </c>
+          <t>Declarado OFICIAL el de 11-Ago (596,249.56, costo completo, tarifa real de la casa). El Sistem (512,859.56) es la referencia operativa del tablero.</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="69" t="inlineStr">
@@ -7926,15 +7938,19 @@
       </c>
       <c r="B17" s="70" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Pago a JM 37,500</t>
         </is>
       </c>
       <c r="C17" s="39" t="inlineStr">
         <is>
-          <t>Fuimos 99, facturadas 97. Cortesías: el padre y la sor (la del director cedida a la sor). Jueves: 27 personas, 19 pagaron 500, 8 sin cobro. Habitaciones de pequeños grupos: 900 × 2 noches. Total 240,220 = avance 23,600 + final 216,620.</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr"/>
+          <t>Desglosado en la hoja de Gastos: transporte 2ª mitad 17,500 (10,000 + 7,500) + desvío 10,000 + ofrenda P. Héctor 10,000.</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>Registrar el desglose en el tablero.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="69" t="inlineStr">
@@ -7944,12 +7960,12 @@
       </c>
       <c r="B18" s="70" t="inlineStr">
         <is>
-          <t>Bizcocho y helados</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="C18" s="39" t="inlineStr">
         <is>
-          <t>Bizcocho de bienvenida 6,000 (10/09, no presupuestado). El bizcocho de la dinámica (ppto Cocina 1,500) se cambió por helados: 1,740 (07/09). La venta de helados del profondo es ingreso, no costo.</t>
+          <t>Fuimos 99, facturadas 97. Cortesías: el padre y la sor (la del director cedida a la sor). Jueves: 27 personas, 19 pagaron 500, 8 sin cobro. Habitaciones de pequeños grupos: 900 × 2 noches. Total 240,220 = avance 23,600 + final 216,620.</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr"/>
@@ -7962,12 +7978,12 @@
       </c>
       <c r="B19" s="70" t="inlineStr">
         <is>
-          <t>Lapiceros e insumos de misa</t>
+          <t>Bizcocho y helados</t>
         </is>
       </c>
       <c r="C19" s="39" t="inlineStr">
         <is>
-          <t>Caja de lapiceros (650) donada; insumos de misa (3,000) asumidos por Jonathan Medina y Fernando Cordero. Ambos en la especie.</t>
+          <t>Bizcocho de bienvenida 6,000 (10/09, no presupuestado). El bizcocho de la dinámica (ppto Cocina 1,500) se cambió por helados: 1,740 (07/09). La venta de helados del profondo es ingreso, no costo.</t>
         </is>
       </c>
       <c r="D19" s="18" t="inlineStr"/>
@@ -7980,12 +7996,12 @@
       </c>
       <c r="B20" s="70" t="inlineStr">
         <is>
-          <t>Impresiones de guías</t>
+          <t>Lapiceros e insumos de misa</t>
         </is>
       </c>
       <c r="C20" s="39" t="inlineStr">
         <is>
-          <t>Mochilas (3,600, pagadas) e "impresiones diversas" (3,600, donadas por Darianny) son trabajos distintos. No hay doble conteo.</t>
+          <t>Caja de lapiceros (650) donada; insumos de misa (3,000) asumidos por Jonathan Medina y Fernando Cordero. Ambos en la especie.</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr"/>
@@ -7998,12 +8014,12 @@
       </c>
       <c r="B21" s="70" t="inlineStr">
         <is>
-          <t>Priscila</t>
+          <t>Impresiones de guías</t>
         </is>
       </c>
       <c r="C21" s="39" t="inlineStr">
         <is>
-          <t>Donó materiales (7,340) y recibió 2,000 en efectivo (21/07). Donación neta 5,340; la especie ya lo descuenta.</t>
+          <t>Mochilas (3,600, pagadas) e "impresiones diversas" (3,600, donadas por Darianny) son trabajos distintos. No hay doble conteo.</t>
         </is>
       </c>
       <c r="D21" s="18" t="inlineStr"/>
@@ -8016,37 +8032,37 @@
       </c>
       <c r="B22" s="70" t="inlineStr">
         <is>
+          <t>Priscila</t>
+        </is>
+      </c>
+      <c r="C22" s="39" t="inlineStr">
+        <is>
+          <t>Donó materiales (7,340) y recibió 2,000 en efectivo (21/07). Donación neta 5,340; la especie ya lo descuenta.</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="69" t="inlineStr">
+        <is>
+          <t>CERRADO</t>
+        </is>
+      </c>
+      <c r="B23" s="70" t="inlineStr">
+        <is>
           <t>Balance 117,611 de la hoja General</t>
         </is>
       </c>
-      <c r="C22" s="39" t="inlineStr">
+      <c r="C23" s="39" t="inlineStr">
         <is>
           <t>Cifra escrita a mano hacia el 11-ago, antes del retiro. No es un segundo balance. El oficial es 36,543.40 → real 34,337.</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D23" s="18" t="inlineStr">
         <is>
           <t>Borrar o anotar esa cifra en la hoja de presupuesto.</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="71" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="B23" s="70" t="inlineStr">
-        <is>
-          <t>Especie</t>
-        </is>
-      </c>
-      <c r="C23" s="39" t="inlineStr">
-        <is>
-          <t>Total 92,405: la hoja de presupuesto solo tenía marcados 30,301 (marcas sin actualizar). Peces (36,000), decoración (10,300), Bono Olé (4,588), insumos de misa (3,000), oficina, lapiceros y cocina no estaban marcados.</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="71" t="inlineStr">
@@ -8056,12 +8072,12 @@
       </c>
       <c r="B24" s="70" t="inlineStr">
         <is>
-          <t>Oficina</t>
+          <t>Especie</t>
         </is>
       </c>
       <c r="C24" s="39" t="inlineStr">
         <is>
-          <t>Costo real 5,306.11 asumido por los directores; en la especie se valora a ppto (2,300) por instrucción del director. Solo informativo.</t>
+          <t>Total 92,405: la hoja de presupuesto solo tenía marcados 30,301 (marcas sin actualizar). Peces (36,000), decoración (10,300), Bono Olé (4,588), insumos de misa (3,000), oficina, lapiceros y cocina no estaban marcados.</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr"/>
@@ -8074,12 +8090,12 @@
       </c>
       <c r="B25" s="70" t="inlineStr">
         <is>
-          <t>Presupuestos "Tentativo"</t>
+          <t>Oficina</t>
         </is>
       </c>
       <c r="C25" s="39" t="inlineStr">
         <is>
-          <t>Ambos quedaron marcados "Tentativo — sujeto a ajustes" (2/7/2026). Lección ETC 89: cerrar el presupuesto formalmente antes del retiro y marcar las donaciones en especie al recibirlas.</t>
+          <t>Costo real 5,306.11 asumido por los directores; en la especie se valora a ppto (2,300) por instrucción del director. Solo informativo.</t>
         </is>
       </c>
       <c r="D25" s="18" t="inlineStr"/>
@@ -8092,15 +8108,33 @@
       </c>
       <c r="B26" s="70" t="inlineStr">
         <is>
+          <t>Presupuestos "Tentativo"</t>
+        </is>
+      </c>
+      <c r="C26" s="39" t="inlineStr">
+        <is>
+          <t>Ambos quedaron marcados "Tentativo — sujeto a ajustes" (2/7/2026). Lección ETC 89: cerrar el presupuesto formalmente antes del retiro y marcar las donaciones en especie al recibirlas.</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="71" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="B27" s="70" t="inlineStr">
+        <is>
           <t>Tablero público</t>
         </is>
       </c>
-      <c r="C26" s="39" t="inlineStr">
+      <c r="C27" s="39" t="inlineStr">
         <is>
           <t>Vista pública: corregido el ancho de las tarjetas y añadida la tarjeta de Profondo (corrección entregada). Falta publicarla.</t>
         </is>
       </c>
-      <c r="D26" s="18" t="inlineStr">
+      <c r="D27" s="18" t="inlineStr">
         <is>
           <t>Publicar la corrección en el tablero.</t>
         </is>
